--- a/artfynd/A 44224-2020 artfynd.xlsx
+++ b/artfynd/A 44224-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44224-2020 artfynd.xlsx
+++ b/artfynd/A 44224-2020 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>118059526</v>
       </c>
       <c r="B3" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 44224-2020 artfynd.xlsx
+++ b/artfynd/A 44224-2020 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>121132067</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44224-2020 artfynd.xlsx
+++ b/artfynd/A 44224-2020 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>121132067</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
